--- a/property_management_forms/037_mixed_use_property_development_application_form--property_management_forms.xlsx
+++ b/property_management_forms/037_mixed_use_property_development_application_form--property_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,82 +525,98 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mixed-Use Property Development Application</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Property Development Type</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Select the type of property development you are applying for</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>property_development_type</t>
+          <t>mixed_use_property_development_application_form_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>property_development_type</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Property Size</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Choose the size of the property</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>property_size</t>
+          <t>mixed_use_property_development_application_form_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>property_size</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Land Use</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select the primary use of the land</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>land_use</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>land_use</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter the address of the property</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mixed_use_property_development_application_form_5</t>
+          <t>contact_name</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mixed-Use Property Development Application</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Contact Name</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter the name of the contact person or organization</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Contact Email</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter the contact person or organization email address</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Contact Phone</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter the contact person or organization phone number</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>property_address</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Property Address</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Confirm the property's address</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>property_owner</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Property Owner</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter the name of the property owner</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,386 +763,130 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>property_status</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Property Status</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Describe the property's current status</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Submission Date</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter the date of submission</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>date_of_application</t>
+          <t>submission_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>date_of_application</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Submission Time</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter the time of submission</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>time_of_application</t>
+          <t>mixed_use_property_development_application_form_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>time_of_application</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Describe your development project</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>mixed_use_property_development_application_form_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Property Type (Confirmation)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Confirm the type of property development</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>property_type</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>property_type</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>property_size</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>property_size</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>mixed_use_property_development_application_form_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Mixed-Use Property Development Application</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>land_use</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>land_use</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>contact_name</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>contact_name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>property_address</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>property_address</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>property_owner</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>property_owner</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>property_status</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>property_status</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1121,10 +901,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1149,7 +929,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>property_development_type_choices</t>
+          <t>mixed_use_property_development_application_form_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1166,7 +946,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>property_development_type_choices</t>
+          <t>mixed_use_property_development_application_form_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1183,7 +963,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>property_development_type_choices</t>
+          <t>mixed_use_property_development_application_form_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1200,7 +980,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>property_size_choices</t>
+          <t>mixed_use_property_development_application_form_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1217,7 +997,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>property_size_choices</t>
+          <t>mixed_use_property_development_application_form_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1234,7 +1014,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>property_size_choices</t>
+          <t>mixed_use_property_development_application_form_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1251,7 +1031,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>land_use_choices</t>
+          <t>mixed_use_property_development_application_form_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1268,7 +1048,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>land_use_choices</t>
+          <t>mixed_use_property_development_application_form_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1285,7 +1065,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>land_use_choices</t>
+          <t>mixed_use_property_development_application_form_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1302,7 +1082,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>mixed_use_property_development_application_form_14_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1319,7 +1099,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>mixed_use_property_development_application_form_14_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1336,7 +1116,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>mixed_use_property_development_application_form_14_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1345,108 +1125,6 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>property_size_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>property_size_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>property_size_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>land_use_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>residential</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>land_use_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>commercial</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>land_use_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>industrial</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>Industrial</t>
         </is>
